--- a/import_template_partner/tests/sample_with_agent.xlsx
+++ b/import_template_partner/tests/sample_with_agent.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -79,19 +79,13 @@
     <t xml:space="preserve">comment</t>
   </si>
   <si>
-    <t xml:space="preserve">customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supplier</t>
-  </si>
-  <si>
     <t xml:space="preserve">agent</t>
   </si>
   <si>
     <t xml:space="preserve">agent_type</t>
   </si>
   <si>
-    <t xml:space="preserve">commission</t>
+    <t xml:space="preserve">commission_id</t>
   </si>
   <si>
     <t xml:space="preserve">settlement</t>
@@ -100,7 +94,7 @@
     <t xml:space="preserve">user_id</t>
   </si>
   <si>
-    <t xml:space="preserve">invoice_group_method_id</t>
+    <t xml:space="preserve">sale_invoicing_grouping_criteria_id</t>
   </si>
   <si>
     <t xml:space="preserve">property_payment_term_id</t>
@@ -121,9 +115,6 @@
     <t xml:space="preserve">property_product_pricelist</t>
   </si>
   <si>
-    <t xml:space="preserve">supplier_pricelist_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ref</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
   </si>
   <si>
     <t xml:space="preserve">Notes from tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">Test commission 10%</t>
@@ -355,23 +343,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AP7"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AM7"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.28"/>
@@ -381,33 +369,27 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="15" style="0" width="8.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="20" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="19.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="18.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="28.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="20.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="37.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="25.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="35.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="34" min="33" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="35" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="40" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="23.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="43" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1023" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="19.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="28.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="20.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="37.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="25.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="35.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="13.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="23.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1021" min="1020" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -486,7 +468,7 @@
       <c r="Z1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="0" t="s">
@@ -495,28 +477,28 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="0" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="0" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="0" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="3" t="s">
@@ -525,47 +507,38 @@
       <c r="AM1" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N2" s="0" t="n">
         <v>958958958</v>
@@ -574,44 +547,41 @@
         <v>666555666</v>
       </c>
       <c r="P2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="X2" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="AF2" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="AM2" s="0" t="s">
         <v>54</v>
-      </c>
-      <c r="X2" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z2" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP2" s="0" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -623,124 +593,115 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T5" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP5" s="0" t="s">
-        <v>70</v>
+        <v>65</v>
+      </c>
+      <c r="AM5" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM6" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="T6" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP6" s="0" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T7" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP7" s="0" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="AM7" s="0" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
